--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>85.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>85</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>60</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>17/08 19:30</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>17/08 19:15</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>50</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>50</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>45</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>22/08 23:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>50</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>23/08 10:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>60</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>55</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>70</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>17/08 14:45</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F14" t="n">
+        <v>2.9</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>24/08 17:15</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>45</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>17/08 13:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F16" t="n">
+        <v>2.9</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>50</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F18" t="n">
+        <v>2.7</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>17/08 16:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>50</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>23/08 23:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>45</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>17/08 13:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F21" t="n">
+        <v>3.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>40</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>17/08 10:15</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="F23" t="n">
+        <v>3.6</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>40</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>17/08 15:15</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F25" t="n">
+        <v>3.2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>45</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,187 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45886.08184286933</v>
+        <v>45886.08184287037</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | FC Polissy</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>FC Polissya Zhytomyr – FC LNZ CherkasyUPL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>17/08 15:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+37,4%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45886.15104721262</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré1re équipe | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Botafogo – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>17/08 23:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+7,19%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45886.15104721262</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Nantes – P</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Nantes – Paris SGLigue 1 McDonald's®</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>17/08 18:45</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+6,23%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45886.15104721262</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | FCV Dender</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FCV Dender EH – AnderlechtBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>17/08 11:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>26,4%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+5,64%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45886.15104721262</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -1580,10 +1580,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>60</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45886.15104721262</v>
+        <v>45886.15104721065</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>17/08 23:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F28" t="n">
+        <v>2.4</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45886.15104721262</v>
+        <v>45886.15104721065</v>
       </c>
     </row>
     <row r="29">
@@ -1670,10 +1666,8 @@
           <t>17/08 18:45</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F29" t="n">
+        <v>2.5</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1686,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45886.15104721262</v>
+        <v>45886.15104721065</v>
       </c>
     </row>
     <row r="30">
@@ -1715,10 +1709,8 @@
           <t>17/08 11:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1731,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45886.15104721262</v>
+        <v>45886.15104721065</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1726,6 +1726,96 @@
         <v>45886.15104721065</v>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 9.5 - tirs1re équipe | Brest – Li</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Brest – LilleLigue 1 McDonald's®</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>17/08 13:00</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45886.22364651482</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | Santa Clar</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Santa Clara – Moreirense FCLiga Portugal</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>17/08 17:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+6,81%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45886.22364651482</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>17/08 13:00</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="F31" t="n">
+        <v>3.2</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45886.22364651482</v>
+        <v>45886.22364651621</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>17/08 17:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>50</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,277 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45886.22364651482</v>
+        <v>45886.22364651621</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | FC Polissy</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FC Polissya Zhytomyr – FC LNZ CherkasyUPL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>17/08 15:00</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>80.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+61,1%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45886.27290447928</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 27.5 - tirs | Mirassol –</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Mirassol – CruzeiroBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>18/08 23:00</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>48,9%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+39,3%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45886.27290447928</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | Van De Zan</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Van De Zandsch – A.WaltonATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>17/08 18:10</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>36,6%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+18,9%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45886.27290447928</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winamax(FR)Football | Plus que 11.5 - tirs2e équipe | Chelsea – </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Chelsea – Crystal PalaceAngleterre - Premier League</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 11.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>17/08 13:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>42,5%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+14,8%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45886.27290447928</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 13.5 - tirs2e équipe | Termalica </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Termalica Bruk-Bet Nieciecza – Rakow CzestochowaPologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Moins que 13.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>17/08 18:15</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2.18</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>51,0%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+11,1%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45886.27290447928</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Botafogo –</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Botafogo – PalmeirasBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>17/08 23:30</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2.23</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+6,96%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45886.27290447928</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>17/08 15:00</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>80.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>80</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45886.27290447928</v>
+        <v>45886.27290447916</v>
       </c>
     </row>
     <row r="34">
@@ -1883,10 +1881,8 @@
           <t>18/08 23:00</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F34" t="n">
+        <v>2.85</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1899,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45886.27290447928</v>
+        <v>45886.27290447916</v>
       </c>
     </row>
     <row r="35">
@@ -1928,10 +1924,8 @@
           <t>17/08 18:10</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
+      <c r="F35" t="n">
+        <v>3.25</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1944,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45886.27290447928</v>
+        <v>45886.27290447916</v>
       </c>
     </row>
     <row r="36">
@@ -1973,10 +1967,8 @@
           <t>17/08 13:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.7</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1989,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45886.27290447928</v>
+        <v>45886.27290447916</v>
       </c>
     </row>
     <row r="37">
@@ -2018,10 +2010,8 @@
           <t>17/08 18:15</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2.18</t>
-        </is>
+      <c r="F37" t="n">
+        <v>2.18</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2034,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45886.27290447928</v>
+        <v>45886.27290447916</v>
       </c>
     </row>
     <row r="38">
@@ -2063,23 +2053,111 @@
           <t>17/08 23:30</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>48,0%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+6,96%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45886.27290447916</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 20.5 - tirs | Espanyol –</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Espanyol – Atlético MadridEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Moins que 20.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>17/08 19:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>33,2%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+9,63%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45886.30597891578</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 14.5 - tirs2e équipe | Wisla Ploc</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wisla Plock – Legia VarsoviePologne - Pologne Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Plus que 14.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>17/08 18:15</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
         <is>
           <t>2.23</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>48,0%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>+6,96%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>45886.27290447928</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>48,6%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+8,30%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45886.30597891578</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>17/08 19:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F39" t="n">
+        <v>3.3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45886.30597891578</v>
+        <v>45886.30597891204</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>17/08 18:15</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.23</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.23</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,187 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45886.30597891578</v>
+        <v>45886.30597891204</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 29.5 - tirs | Glasgow Ra</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Glasgow Rangers – Club BrugesEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Plus que 29.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+23,8%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45886.35334408371</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis | 2 - aces | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Carlos AlcarazATP - Cincinnati</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2 - aces</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>62,4%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45886.35334408371</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | ASC Otelul</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ASC Otelul Galati – CFR ClujLiga 1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>24/08 13:15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2,30%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+15,1%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45886.35334408371</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Internacional – FlamengoSérie A</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>17/08 21:30</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2,18%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+8,87%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45886.35334408371</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2182,10 +2182,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.7</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45886.35334408371</v>
+        <v>45886.35334408565</v>
       </c>
     </row>
     <row r="42">
@@ -2227,10 +2225,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F42" t="n">
+        <v>1.85</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2243,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45886.35334408371</v>
+        <v>45886.35334408565</v>
       </c>
     </row>
     <row r="43">
@@ -2272,10 +2268,8 @@
           <t>24/08 13:15</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F43" t="n">
+        <v>50</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2288,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45886.35334408371</v>
+        <v>45886.35334408565</v>
       </c>
     </row>
     <row r="44">
@@ -2317,10 +2311,8 @@
           <t>17/08 21:30</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F44" t="n">
+        <v>50</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2333,7 +2325,277 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45886.35334408371</v>
+        <v>45886.35334408565</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | FC La Tour</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>FC La Tour-Le Paquier – FC Stade NyonnaisCoupe de Suisse</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>17/08 13:00</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>70.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+54,8%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45886.39023419518</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CA Banfiel</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CA Banfield – Estudiantes de La PlataLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>17/08 19:15</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+43,0%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45886.39023419518</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | H.Medjedov</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>H.Medjedovic – A.RinderknechATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>17/08 20:10</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>22,1%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+32,6%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45886.39023419518</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 23.5 - tirs | Internacio</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Internacional RS – FlamengoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Moins que 23.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>17/08 21:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>39,4%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+12,3%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45886.39023419518</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 20.5 - tirs | Athletic B</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Athletic Bilbao – SévilleEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 20.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>17/08 17:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>38,0%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+10,2%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45886.39023419518</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs1re équipe | Ferencváro</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ferencvárosi TC – QarabağEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>59,5%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+8,31%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45886.39023419518</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2354,10 +2354,8 @@
           <t>17/08 13:00</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>70.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>70</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2370,7 +2368,7 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45886.39023419518</v>
+        <v>45886.39023418981</v>
       </c>
     </row>
     <row r="46">
@@ -2399,10 +2397,8 @@
           <t>17/08 19:15</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>60</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2415,7 +2411,7 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45886.39023419518</v>
+        <v>45886.39023418981</v>
       </c>
     </row>
     <row r="47">
@@ -2444,10 +2440,8 @@
           <t>17/08 20:10</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>6</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2460,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45886.39023419518</v>
+        <v>45886.39023418981</v>
       </c>
     </row>
     <row r="48">
@@ -2489,10 +2483,8 @@
           <t>17/08 21:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.85</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2505,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45886.39023419518</v>
+        <v>45886.39023418981</v>
       </c>
     </row>
     <row r="49">
@@ -2534,10 +2526,8 @@
           <t>17/08 17:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.9</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2550,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45886.39023419518</v>
+        <v>45886.39023418981</v>
       </c>
     </row>
     <row r="50">
@@ -2579,10 +2569,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
+      <c r="F50" t="n">
+        <v>1.82</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2595,7 +2583,52 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45886.39023419518</v>
+        <v>45886.39023418981</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 18.5 - tirs2e équipe | Nantes – P</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Nantes – Paris SGFrance - Ligue 1 McDonald’s®</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Plus que 18.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>17/08 18:45</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45886.43216436632</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2612,23 +2612,201 @@
           <t>17/08 18:45</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>43,5%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+19,6%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45886.43216436342</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 18.5 - tirs2e équipe | Nantes – P</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Nantes – Paris SGLigue 1 McDonald's®</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Plus que 18.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>17/08 18:45</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
         <is>
           <t>2.75</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>43,5%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>+19,6%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>45886.43216436632</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>43,0%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+18,1%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45886.47068271771</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 24.5 | Musetti L/</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Musetti L/Sonego L – Mektic N / Ram RATP 1000 Cincinnati - Doubles (H)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 24.5</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>17/08 22:00</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>20,7%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+9,84%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45886.47068271771</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 0.5 | RSV Eintra</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>RSV Eintracht Stahnsdorf 1949 – KaiserslauternCoupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Moins que 0.5</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>17/08 13:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>65.00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1,69%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+9,60%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45886.47068271771</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 5.51er set1er participant | Mackenzie </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Mackenzie McDonald – Brandon HoltATP 250 Winston Salem</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Moins que 5.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>17/08 23:40</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>28,0%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+9,34%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45886.47068271771</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>17/08 18:45</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.75</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45886.47068271771</v>
+        <v>45886.4706827199</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>17/08 22:00</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>5.30</t>
-        </is>
+      <c r="F53" t="n">
+        <v>5.3</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45886.47068271771</v>
+        <v>45886.4706827199</v>
       </c>
     </row>
     <row r="54">
@@ -2745,10 +2741,8 @@
           <t>17/08 13:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>65.00</t>
-        </is>
+      <c r="F54" t="n">
+        <v>65</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2761,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45886.47068271771</v>
+        <v>45886.4706827199</v>
       </c>
     </row>
     <row r="55">
@@ -2790,10 +2784,8 @@
           <t>17/08 23:40</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="F55" t="n">
+        <v>3.9</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2806,7 +2798,52 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45886.47068271771</v>
+        <v>45886.4706827199</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Tennis | Moins que 4.51er set1er participant | Mackenzie </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Mackenzie McDonald – Brandon Holt385076e7 ATP 250 Winston Salem</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>17/08 23:40</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>4.30</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>25,9%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+11,3%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45886.52966356849</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2827,10 +2827,8 @@
           <t>17/08 23:40</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>4.30</t>
-        </is>
+      <c r="F56" t="n">
+        <v>4.3</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2843,7 +2841,97 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45886.52966356849</v>
+        <v>45886.52966356481</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tir cadré | Cercle Bru</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Cercle Bruges – WesterloBelgique - Belgique Division 1A</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>17/08 17:15</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>44,3%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+6,29%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45886.56256159243</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Machida Ze</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Machida Zelvia – Gamba OsakaJ-League</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>20/08 10:00</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2,11%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+5,67%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45886.56256159243</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I58"/>
+  <dimension ref="A1:I60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>17/08 17:15</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
+      <c r="F57" t="n">
+        <v>2.4</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45886.56256159243</v>
+        <v>45886.56256159722</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>20/08 10:00</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F58" t="n">
+        <v>50</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,97 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45886.56256159243</v>
+        <v>45886.56256159722</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | CFR Cluj –</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CFR Cluj – FC BotosaniLiga 1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>17/08 15:30</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+23,7%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45886.59704985896</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 4.51er set2e participant | Katrina Sc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Katrina Scott – Polina KudermetovaWTA 250 Cleveland</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Moins que 4.51er set2e participant</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>17/08 19:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>29,8%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+4,48%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45886.59704985896</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I60"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2956,10 +2956,8 @@
           <t>17/08 15:30</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F59" t="n">
+        <v>55</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2972,7 +2970,7 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45886.59704985896</v>
+        <v>45886.59704986111</v>
       </c>
     </row>
     <row r="60">
@@ -3001,10 +2999,8 @@
           <t>17/08 19:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F60" t="n">
+        <v>3.5</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3017,7 +3013,97 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45886.59704985896</v>
+        <v>45886.59704986111</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | IF Elfsbor</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>IF Elfsborg – Halmstads BKAllsvenskan</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>24/08 14:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+8,42%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45886.63960589876</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | Moins que 20.5 - tirs | Athletic B</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Athletic Bilbao – FC SévilleEspagne - LaLiga</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 20.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>17/08 17:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>38,7%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+4,54%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45886.63960589876</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I62"/>
+  <dimension ref="A1:I63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3042,10 +3042,8 @@
           <t>24/08 14:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F61" t="n">
+        <v>50</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3058,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45886.63960589876</v>
+        <v>45886.63960590278</v>
       </c>
     </row>
     <row r="62">
@@ -3087,10 +3085,8 @@
           <t>17/08 17:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F62" t="n">
+        <v>2.7</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3103,7 +3099,52 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45886.63960589876</v>
+        <v>45886.63960590278</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Austria Vi</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Austria Vienne – TSV HartbergBundesliga</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+14,6%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45886.6849616535</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I63"/>
+  <dimension ref="A1:I64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3128,10 +3128,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F63" t="n">
+        <v>50</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3144,7 +3142,52 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45886.6849616535</v>
+        <v>45886.68496165509</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 8.5 - tir cadré | Elche – Be</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Elche – BetisEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 8.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>36,4%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+5,42%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45886.72145110705</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,10 +3171,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F64" t="n">
+        <v>2.9</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3187,7 +3185,187 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45886.72145110705</v>
+        <v>45886.72145111111</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Crystal Pa</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Crystal Palace – FredrikstadLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+21,3%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45886.77136206714</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 22.5 | Guo H/Pano</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Guo H/Panova A – Dabrowski G/Routliffe EWTA 1000 Cincinnati - Doubles</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 22.5</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>17/08 23:30</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>4.05</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>26,3%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+6,33%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45886.77136206714</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | KFC Komarn</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>KFC Komarno – Spartak TrnavaFortuna Liga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>24/08 15:00</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+6,08%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45886.77136206714</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Leixoes SC</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Leixoes SC – FC PenafielPortugal, Segunda Liga</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>24/08 13:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>40.00</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+6,02%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45886.77136206714</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I68"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3214,10 +3214,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F65" t="n">
+        <v>60</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3230,7 +3228,7 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45886.77136206714</v>
+        <v>45886.77136207176</v>
       </c>
     </row>
     <row r="66">
@@ -3259,10 +3257,8 @@
           <t>17/08 23:30</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>4.05</t>
-        </is>
+      <c r="F66" t="n">
+        <v>4.05</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3275,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45886.77136206714</v>
+        <v>45886.77136207176</v>
       </c>
     </row>
     <row r="67">
@@ -3304,10 +3300,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>40</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3320,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45886.77136206714</v>
+        <v>45886.77136207176</v>
       </c>
     </row>
     <row r="68">
@@ -3349,10 +3343,8 @@
           <t>24/08 13:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>40.00</t>
-        </is>
+      <c r="F68" t="n">
+        <v>40</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3365,7 +3357,187 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45886.77136206714</v>
+        <v>45886.77136207176</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar – ZwolleEredivisie</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>24/08 10:15</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+8,86%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45886.80393844726</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | Pas de buts | Wehen Wies</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Wehen Wiesbaden – Bayern MunichAllemagne. Coupe d'Allemagne</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>27/08 18:45</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1,97%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+8,43%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45886.80393844726</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 9.5 - tir cadré | Elche – Be</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Elche – BetisEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+5,67%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45886.80393844726</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 23.5 | Musetti L/</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Musetti L/Sonego L – Mektic N / Ram RATP 1000 Cincinnati - Doubles (H)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Plus que 23.5</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>17/08 22:00</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>25,2%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+4,59%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45886.80393844726</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I72"/>
+  <dimension ref="A1:I74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,10 +3386,8 @@
           <t>24/08 10:15</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>60</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3402,7 +3400,7 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45886.80393844726</v>
+        <v>45886.80393844908</v>
       </c>
     </row>
     <row r="70">
@@ -3431,10 +3429,8 @@
           <t>27/08 18:45</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F70" t="n">
+        <v>55</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3447,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45886.80393844726</v>
+        <v>45886.80393844908</v>
       </c>
     </row>
     <row r="71">
@@ -3476,10 +3472,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F71" t="n">
+        <v>4.25</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3492,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45886.80393844726</v>
+        <v>45886.80393844908</v>
       </c>
     </row>
     <row r="72">
@@ -3521,10 +3515,8 @@
           <t>17/08 22:00</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>4.15</t>
-        </is>
+      <c r="F72" t="n">
+        <v>4.15</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3537,7 +3529,97 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45886.80393844726</v>
+        <v>45886.80393844908</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Remplaçant marque un but: Oui | Real Madri</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Real Madrid – OsasunaLaLiga</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Remplaçant marque un but: Oui</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>41,7%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+4,16%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45886.85023496573</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 24.5 - tirs | Kasimpasa </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Kasimpasa – TrabzonsporTurquie - Turquie Super Lig</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>18/08 18:30</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+3,38%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45886.85023496573</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:I78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3558,10 +3558,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.5</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3574,7 +3572,7 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45886.85023496573</v>
+        <v>45886.85023496528</v>
       </c>
     </row>
     <row r="74">
@@ -3603,10 +3601,8 @@
           <t>18/08 18:30</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F74" t="n">
+        <v>2.9</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3619,7 +3615,187 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45886.85023496573</v>
+        <v>45886.85023496528</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 9.5 - tirs1re équipe | Internacio</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Internacional RS – FlamengoBrésil - Brésil Série A</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>17/08 21:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>36,9%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+8,76%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45886.88917707272</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Club Gener</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Club General Caballero JLM – Club OlimpiaPrimera Division</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>24/08 19:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+8,49%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45886.88917707272</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Jannik Sin</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Jannik Sinner – Carlos AlcarazATP 1000 Cincinnati</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>18/08 19:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>5.70</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>18,8%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+7,39%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45886.88917707272</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 5.5 - tir cadré1re équipe | Etoile Rou</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Etoile Rouge Belgrade – Pafos FCEurope - Ligue des Champions</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>19/08 19:00</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>50,9%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+1,82%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45886.88917707272</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3644,10 +3644,8 @@
           <t>17/08 21:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F75" t="n">
+        <v>2.95</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3660,7 +3658,7 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45886.88917707272</v>
+        <v>45886.88917707176</v>
       </c>
     </row>
     <row r="76">
@@ -3689,10 +3687,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>45</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3705,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45886.88917707272</v>
+        <v>45886.88917707176</v>
       </c>
     </row>
     <row r="77">
@@ -3734,10 +3730,8 @@
           <t>18/08 19:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>5.70</t>
-        </is>
+      <c r="F77" t="n">
+        <v>5.7</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3750,7 +3744,7 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45886.88917707272</v>
+        <v>45886.88917707176</v>
       </c>
     </row>
     <row r="78">
@@ -3779,10 +3773,8 @@
           <t>19/08 19:00</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
+      <c r="F78" t="n">
+        <v>2</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3795,7 +3787,232 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45886.88917707272</v>
+        <v>45886.88917707176</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Cerro Port</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Cerro Porteno – Sportivo TrinidensePrimera Division</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>24/08 21:30</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2,20%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45886.93134011012</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.52e équipe | Breidablik</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Breidablik – SS VirtusLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Plus que 2.52e équipe</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+9,18%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45886.93134011012</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Pumas Unam</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Pumas Unam – Club PueblaLiga MX</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>24/08 23:00</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+2,24%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45886.93134011012</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Plus que 6.51er set1er participant | Aleksandar</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Aleksandar Kovacevic – Filip MisolicATP 250 Winston Salem</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Plus que 6.51er set1er participant</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>18/08 19:10</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>6.20</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+1,71%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45886.93134011012</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball | X(12:0)P | Monténégro</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Monténégro – AllemagneBasket FIBA. EuroBasket</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>X(12:0)P</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>27/08 13:30</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>+0,37%</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>45886.93134011012</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-17.xlsx
+++ b/data/valuebets_database_2025-08-17.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3816,10 +3816,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>50</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3832,7 +3830,7 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45886.93134011012</v>
+        <v>45886.93134011574</v>
       </c>
     </row>
     <row r="80">
@@ -3861,10 +3859,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F80" t="n">
+        <v>45</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3877,7 +3873,7 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45886.93134011012</v>
+        <v>45886.93134011574</v>
       </c>
     </row>
     <row r="81">
@@ -3906,10 +3902,8 @@
           <t>24/08 23:00</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>50</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3922,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45886.93134011012</v>
+        <v>45886.93134011574</v>
       </c>
     </row>
     <row r="82">
@@ -3951,10 +3945,8 @@
           <t>18/08 19:10</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>6.20</t>
-        </is>
+      <c r="F82" t="n">
+        <v>6.2</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3967,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45886.93134011012</v>
+        <v>45886.93134011574</v>
       </c>
     </row>
     <row r="83">
@@ -3996,10 +3988,8 @@
           <t>27/08 13:30</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F83" t="n">
+        <v>20</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -4012,7 +4002,52 @@
         </is>
       </c>
       <c r="I83" s="2" t="n">
-        <v>45886.93134011012</v>
+        <v>45886.93134011574</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Millonario</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Millonarios FC – Atletico JuniorPrimera A</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>24/08 01:30</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>+2,38%</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>45886.97295214778</v>
       </c>
     </row>
   </sheetData>
